--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,9 +785,365 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135791303</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bursjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>559251</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6827102</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Undersvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791303</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135791304</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bursjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559236</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6827166</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Undersvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791304</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135856150</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bursjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559252</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6827100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undersvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135856150</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135791303</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135791304</v>
       </c>
       <c r="B4" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33032-2026 artfynd.xlsx
+++ b/artfynd/A 33032-2026 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>135856150</v>
       </c>
       <c r="B5" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
